--- a/outputs/evaluation/decision/v2/CF_M05/run_3/CF_M05_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M05/run_3/CF_M05_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,83 +471,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M05_C11</t>
+          <t>CF_M05_C09 , *CF_M05_C11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Confidentiality</t>
+          <t>Integrity; Confidentiality</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Access Control Microservice</t>
+          <t>Leader Microservice</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications, specifically blocking any unauthorized connection attempt and applying certain security protocols to prevent improper access and possible vulnerabilities.</t>
+          <t>AWS invests heavily in security and certifications, manages multiple levels of security and offers tools to protect data and infrastructures facilitating compliance with legal regulations and international standards.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.7252</v>
+        <v>0.7018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>CF_M05_C01, *CF_M05_C12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU02</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Appearance; Visual and Functional consistency</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Communication Log Microservice</t>
+          <t>Portal Microservice</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -557,50 +557,50 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications, specifically blocking any unauthorized connection attempt and applying certain security protocols to prevent improper access and possible vulnerabilities.</t>
+          <t>The use of this architecture allows high scalability, availability, and accessibility, as resource management can be done according to needs and anywhere with an Internet connection.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7118</v>
+        <v>0.6857</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>*CF_M05_C11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Presentation and user experience</t>
+          <t>Confidentiality</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Access Control Microservice</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -609,198 +609,342 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8676</v>
+        <v>0.6688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>*CF_M05_C13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Capacity; Maintainability; Scalability</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Communication Log Microservice</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The use of this architecture allows high scalability, availability, and accessibility, since the management of resources can be done according to needs and anywhere with an Internet connection.</t>
+          <t>AWS invests heavily in security and certifications, manages multiple levels of security and offers tools to protect data and infrastructures facilitating compliance with legal regulations and international standards.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.7214</v>
+        <v>0.6661</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M05_C14</t>
+          <t>*CF_M05_C15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Presentation and user experience</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Angular; Spring Boot</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated. This structure clarifies roles, avoids unnecessary coupling, and facilitates testing, reusing, and maintaining the code over time.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.7083</v>
+        <v>0.8676</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AD11</t>
+          <t>CF_M05_AD09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Availability; Capacity</t>
+          <t>Capacity; Maintainability; Scalability</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Amazon EKS</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The use of this architecture allows high scalability, availability, and accessibility, since the management of resources can be done according to needs and anywhere with an Internet connection.</t>
+          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.7876</v>
+        <v>0.7176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>77</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Angular; Spring Boot</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Angular applies the MVVM pattern, as its architecture is based on components and services.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6804</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>81</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Availability; Capacity</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>The use of this architecture allows high scalability, availability, and accessibility, as resource management can be done according to needs and anywhere with an Internet connection.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7877999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>*CF_M05_C14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU29</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>78</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spring Boot</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7494</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>CF_M05_AD13</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>*CF_M05_C18</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E11" t="n">
         <v>82</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Scalability</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>AD_01</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J11" t="n">
         <v>0.767</v>
       </c>
     </row>
